--- a/data/externalStats/File1/RPT_RPT5219538410918ZM_externalStats.xlsx
+++ b/data/externalStats/File1/RPT_RPT5219538410918ZM_externalStats.xlsx
@@ -2104,7 +2104,7 @@
         <v>28321838.53519511</v>
       </c>
       <c r="AI25" s="46" t="n">
-        <v>37842.212106</v>
+        <v>37842.21210599999</v>
       </c>
       <c r="AK25" s="120" t="n">
         <v>1</v>
@@ -2197,7 +2197,7 @@
         </is>
       </c>
       <c r="AN26" s="58" t="n">
-        <v>596.3959799999999</v>
+        <v>596.3959799999998</v>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1" thickBot="1">
@@ -2332,7 +2332,7 @@
         </is>
       </c>
       <c r="AH28" s="122" t="n">
-        <v>9782432.197343033</v>
+        <v>9782432.197343031</v>
       </c>
       <c r="AI28" s="56" t="n">
         <v>486.1268050000001</v>
@@ -2409,7 +2409,7 @@
         </is>
       </c>
       <c r="AH29" s="122" t="n">
-        <v>8455132.003897959</v>
+        <v>8455132.003897958</v>
       </c>
       <c r="AI29" s="56" t="n">
         <v>653.7931000000001</v>
@@ -2620,7 +2620,7 @@
         </is>
       </c>
       <c r="AH32" s="122" t="n">
-        <v>5634318.81464013</v>
+        <v>5634318.814640129</v>
       </c>
       <c r="AI32" s="56" t="n">
         <v>752.332995</v>
@@ -2697,7 +2697,7 @@
         </is>
       </c>
       <c r="AH33" s="122" t="n">
-        <v>3525876.647080136</v>
+        <v>3525876.647080135</v>
       </c>
       <c r="AI33" s="56" t="n">
         <v>12388.239665</v>
@@ -2928,7 +2928,7 @@
         </is>
       </c>
       <c r="AH36" s="122" t="n">
-        <v>2790844.477037583</v>
+        <v>2790844.477037584</v>
       </c>
       <c r="AI36" s="56" t="n">
         <v>340.605115</v>
@@ -3446,7 +3446,7 @@
         <v>1553571.067329031</v>
       </c>
       <c r="AI43" s="56" t="n">
-        <v>3118.807607</v>
+        <v>3118.807607000001</v>
       </c>
       <c r="AK43" s="123" t="n">
         <v>19</v>
@@ -4447,7 +4447,7 @@
         <v>1378098.727412944</v>
       </c>
       <c r="AH59" s="56" t="n">
-        <v>4568.302288</v>
+        <v>4568.302287999999</v>
       </c>
     </row>
     <row r="60">
@@ -4715,49 +4715,49 @@
         <v>0</v>
       </c>
       <c r="J63" s="130" t="n">
-        <v>1964.875071784408</v>
+        <v>1964.875071784404</v>
       </c>
       <c r="K63" s="131" t="n">
-        <v>347.8756485030455</v>
+        <v>347.8756485030452</v>
       </c>
       <c r="L63" s="131" t="n">
         <v>130.6682137649017</v>
       </c>
       <c r="M63" s="131" t="n">
-        <v>663.9327169755762</v>
+        <v>663.9327169755763</v>
       </c>
       <c r="N63" s="132" t="n">
-        <v>3107.351651027931</v>
+        <v>3107.351651027927</v>
       </c>
       <c r="P63" s="130" t="n">
-        <v>2163.155319482375</v>
+        <v>2163.15531948237</v>
       </c>
       <c r="Q63" s="131" t="n">
-        <v>372.0859813343213</v>
+        <v>372.085981334321</v>
       </c>
       <c r="R63" s="131" t="n">
-        <v>143.0165673943964</v>
+        <v>143.0165673943963</v>
       </c>
       <c r="S63" s="131" t="n">
-        <v>753.6182474419384</v>
+        <v>753.6182474419385</v>
       </c>
       <c r="T63" s="132" t="n">
-        <v>3431.876115653031</v>
+        <v>3431.876115653025</v>
       </c>
       <c r="V63" s="130" t="n">
-        <v>2378.866087308555</v>
+        <v>2378.86608730855</v>
       </c>
       <c r="W63" s="131" t="n">
-        <v>407.7078036315904</v>
+        <v>407.7078036315899</v>
       </c>
       <c r="X63" s="131" t="n">
         <v>157.7761316534635</v>
       </c>
       <c r="Y63" s="131" t="n">
-        <v>854.1693686244979</v>
+        <v>854.1693686244978</v>
       </c>
       <c r="Z63" s="132" t="n">
-        <v>3798.519391218107</v>
+        <v>3798.519391218101</v>
       </c>
       <c r="AE63" s="121" t="n">
         <v>15</v>
@@ -5126,49 +5126,49 @@
         <v>0</v>
       </c>
       <c r="J68" s="142" t="n">
-        <v>1964.875071784408</v>
+        <v>1964.875071784404</v>
       </c>
       <c r="K68" s="143" t="n">
-        <v>347.8756485030455</v>
+        <v>347.8756485030452</v>
       </c>
       <c r="L68" s="143" t="n">
         <v>130.6682137649017</v>
       </c>
       <c r="M68" s="143" t="n">
-        <v>663.9327169755762</v>
+        <v>663.9327169755763</v>
       </c>
       <c r="N68" s="144" t="n">
-        <v>3107.351651027931</v>
+        <v>3107.351651027927</v>
       </c>
       <c r="P68" s="142" t="n">
-        <v>2163.155319482375</v>
+        <v>2163.15531948237</v>
       </c>
       <c r="Q68" s="143" t="n">
-        <v>372.0859813343213</v>
+        <v>372.085981334321</v>
       </c>
       <c r="R68" s="143" t="n">
-        <v>143.0165673943964</v>
+        <v>143.0165673943963</v>
       </c>
       <c r="S68" s="143" t="n">
-        <v>753.6182474419384</v>
+        <v>753.6182474419385</v>
       </c>
       <c r="T68" s="144" t="n">
-        <v>3431.876115653031</v>
+        <v>3431.876115653025</v>
       </c>
       <c r="V68" s="142" t="n">
-        <v>2378.866087308555</v>
+        <v>2378.86608730855</v>
       </c>
       <c r="W68" s="143" t="n">
-        <v>407.7078036315904</v>
+        <v>407.7078036315899</v>
       </c>
       <c r="X68" s="143" t="n">
         <v>157.7761316534635</v>
       </c>
       <c r="Y68" s="143" t="n">
-        <v>854.1693686244979</v>
+        <v>854.1693686244978</v>
       </c>
       <c r="Z68" s="144" t="n">
-        <v>3798.519391218107</v>
+        <v>3798.519391218101</v>
       </c>
       <c r="AE68" s="124" t="n">
         <v>20</v>
@@ -7211,49 +7211,49 @@
         <v>0</v>
       </c>
       <c r="J99" s="130" t="n">
-        <v>1964.875071784408</v>
+        <v>1964.875071784404</v>
       </c>
       <c r="K99" s="131" t="n">
-        <v>347.8756485030455</v>
+        <v>347.8756485030452</v>
       </c>
       <c r="L99" s="131" t="n">
         <v>130.6682137649017</v>
       </c>
       <c r="M99" s="131" t="n">
-        <v>663.9327169755762</v>
+        <v>663.9327169755763</v>
       </c>
       <c r="N99" s="132" t="n">
-        <v>3107.351651027931</v>
+        <v>3107.351651027927</v>
       </c>
       <c r="P99" s="130" t="n">
-        <v>2163.155319482375</v>
+        <v>2163.15531948237</v>
       </c>
       <c r="Q99" s="131" t="n">
-        <v>372.0859813343213</v>
+        <v>372.085981334321</v>
       </c>
       <c r="R99" s="131" t="n">
-        <v>143.0165673943964</v>
+        <v>143.0165673943963</v>
       </c>
       <c r="S99" s="131" t="n">
-        <v>753.6182474419384</v>
+        <v>753.6182474419385</v>
       </c>
       <c r="T99" s="132" t="n">
-        <v>3431.876115653031</v>
+        <v>3431.876115653025</v>
       </c>
       <c r="V99" s="130" t="n">
-        <v>2378.866087308555</v>
+        <v>2378.86608730855</v>
       </c>
       <c r="W99" s="131" t="n">
-        <v>407.7078036315904</v>
+        <v>407.7078036315899</v>
       </c>
       <c r="X99" s="131" t="n">
         <v>157.7761316534635</v>
       </c>
       <c r="Y99" s="131" t="n">
-        <v>854.1693686244979</v>
+        <v>854.1693686244978</v>
       </c>
       <c r="Z99" s="132" t="n">
-        <v>3798.519391218107</v>
+        <v>3798.519391218101</v>
       </c>
     </row>
     <row r="100">
@@ -7550,49 +7550,49 @@
         <v>0</v>
       </c>
       <c r="J104" s="142" t="n">
-        <v>1964.875071784408</v>
+        <v>1964.875071784404</v>
       </c>
       <c r="K104" s="143" t="n">
-        <v>347.8756485030455</v>
+        <v>347.8756485030452</v>
       </c>
       <c r="L104" s="143" t="n">
         <v>130.6682137649017</v>
       </c>
       <c r="M104" s="143" t="n">
-        <v>663.9327169755762</v>
+        <v>663.9327169755763</v>
       </c>
       <c r="N104" s="144" t="n">
-        <v>3107.351651027931</v>
+        <v>3107.351651027927</v>
       </c>
       <c r="P104" s="142" t="n">
-        <v>2163.155319482375</v>
+        <v>2163.15531948237</v>
       </c>
       <c r="Q104" s="143" t="n">
-        <v>372.0859813343213</v>
+        <v>372.085981334321</v>
       </c>
       <c r="R104" s="143" t="n">
-        <v>143.0165673943964</v>
+        <v>143.0165673943963</v>
       </c>
       <c r="S104" s="143" t="n">
-        <v>753.6182474419384</v>
+        <v>753.6182474419385</v>
       </c>
       <c r="T104" s="144" t="n">
-        <v>3431.876115653031</v>
+        <v>3431.876115653025</v>
       </c>
       <c r="V104" s="142" t="n">
-        <v>2378.866087308555</v>
+        <v>2378.86608730855</v>
       </c>
       <c r="W104" s="143" t="n">
-        <v>407.7078036315904</v>
+        <v>407.7078036315899</v>
       </c>
       <c r="X104" s="143" t="n">
         <v>157.7761316534635</v>
       </c>
       <c r="Y104" s="143" t="n">
-        <v>854.1693686244979</v>
+        <v>854.1693686244978</v>
       </c>
       <c r="Z104" s="144" t="n">
-        <v>3798.519391218107</v>
+        <v>3798.519391218101</v>
       </c>
     </row>
     <row r="105" ht="30.3" customHeight="1" thickBot="1"/>
@@ -8644,7 +8644,7 @@
         </is>
       </c>
       <c r="AN25" s="48" t="n">
-        <v>98.91374267056</v>
+        <v>98.91374267056001</v>
       </c>
     </row>
     <row r="26">
@@ -8859,7 +8859,7 @@
         <v>10108103.37976938</v>
       </c>
       <c r="AI28" s="56" t="n">
-        <v>495.2368213257</v>
+        <v>495.2368213256999</v>
       </c>
       <c r="AK28" s="123" t="n">
         <v>4</v>
@@ -8936,7 +8936,7 @@
         <v>9576725.592281302</v>
       </c>
       <c r="AI29" s="56" t="n">
-        <v>683.19083598375</v>
+        <v>683.1908359837498</v>
       </c>
       <c r="AK29" s="123" t="n">
         <v>5</v>
@@ -9010,7 +9010,7 @@
         </is>
       </c>
       <c r="AH30" s="122" t="n">
-        <v>8736615.461358383</v>
+        <v>8736615.461358385</v>
       </c>
       <c r="AI30" s="56" t="n">
         <v>666.0451826940001</v>
@@ -9144,7 +9144,7 @@
         </is>
       </c>
       <c r="AH32" s="122" t="n">
-        <v>7261041.493413353</v>
+        <v>7261041.493413352</v>
       </c>
       <c r="AI32" s="56" t="n">
         <v>911.6395066912501</v>
@@ -9221,7 +9221,7 @@
         </is>
       </c>
       <c r="AH33" s="122" t="n">
-        <v>4000601.555590694</v>
+        <v>4000601.555590695</v>
       </c>
       <c r="AI33" s="56" t="n">
         <v>13968.60739906405</v>
@@ -9317,7 +9317,7 @@
         </is>
       </c>
       <c r="AN34" s="58" t="n">
-        <v>4214.04076808376</v>
+        <v>4214.040768083759</v>
       </c>
     </row>
     <row r="35" ht="15" customHeight="1" thickBot="1">
@@ -9606,7 +9606,7 @@
         </is>
       </c>
       <c r="AH38" s="122" t="n">
-        <v>2230525.508568965</v>
+        <v>2230525.508568964</v>
       </c>
       <c r="AI38" s="56" t="n">
         <v>2223.40933748808</v>
@@ -9672,7 +9672,7 @@
         <v>2065048.249427686</v>
       </c>
       <c r="AI39" s="56" t="n">
-        <v>386.735912532</v>
+        <v>386.7359125319999</v>
       </c>
       <c r="AK39" s="123" t="n">
         <v>15</v>
@@ -10280,7 +10280,7 @@
         </is>
       </c>
       <c r="AG51" s="122" t="n">
-        <v>9888326.187878197</v>
+        <v>9888326.187878195</v>
       </c>
       <c r="AH51" s="56" t="n">
         <v>5005.6285081715</v>
@@ -10968,7 +10968,7 @@
         </is>
       </c>
       <c r="AG59" s="122" t="n">
-        <v>1611604.857738647</v>
+        <v>1611604.857738646</v>
       </c>
       <c r="AH59" s="56" t="n">
         <v>420.2046113878201</v>
@@ -11239,49 +11239,49 @@
         <v>0</v>
       </c>
       <c r="J63" s="130" t="n">
-        <v>1964.875071784408</v>
+        <v>1964.875071784404</v>
       </c>
       <c r="K63" s="131" t="n">
-        <v>347.8756485030455</v>
+        <v>347.8756485030452</v>
       </c>
       <c r="L63" s="131" t="n">
         <v>130.6682137649017</v>
       </c>
       <c r="M63" s="131" t="n">
-        <v>663.9327169755762</v>
+        <v>663.9327169755763</v>
       </c>
       <c r="N63" s="132" t="n">
-        <v>3107.351651027931</v>
+        <v>3107.351651027927</v>
       </c>
       <c r="P63" s="130" t="n">
-        <v>2163.155319482375</v>
+        <v>2163.15531948237</v>
       </c>
       <c r="Q63" s="131" t="n">
-        <v>372.0859813343213</v>
+        <v>372.085981334321</v>
       </c>
       <c r="R63" s="131" t="n">
-        <v>143.0165673943964</v>
+        <v>143.0165673943963</v>
       </c>
       <c r="S63" s="131" t="n">
-        <v>753.6182474419384</v>
+        <v>753.6182474419385</v>
       </c>
       <c r="T63" s="132" t="n">
-        <v>3431.876115653031</v>
+        <v>3431.876115653025</v>
       </c>
       <c r="V63" s="130" t="n">
-        <v>2378.866087308555</v>
+        <v>2378.86608730855</v>
       </c>
       <c r="W63" s="131" t="n">
-        <v>407.7078036315904</v>
+        <v>407.7078036315899</v>
       </c>
       <c r="X63" s="131" t="n">
         <v>157.7761316534635</v>
       </c>
       <c r="Y63" s="131" t="n">
-        <v>854.1693686244979</v>
+        <v>854.1693686244978</v>
       </c>
       <c r="Z63" s="132" t="n">
-        <v>3798.519391218107</v>
+        <v>3798.519391218101</v>
       </c>
       <c r="AE63" s="121" t="n">
         <v>15</v>
@@ -11650,49 +11650,49 @@
         <v>0</v>
       </c>
       <c r="J68" s="142" t="n">
-        <v>1964.875071784408</v>
+        <v>1964.875071784404</v>
       </c>
       <c r="K68" s="143" t="n">
-        <v>347.8756485030455</v>
+        <v>347.8756485030452</v>
       </c>
       <c r="L68" s="143" t="n">
         <v>130.6682137649017</v>
       </c>
       <c r="M68" s="143" t="n">
-        <v>663.9327169755762</v>
+        <v>663.9327169755763</v>
       </c>
       <c r="N68" s="144" t="n">
-        <v>3107.351651027931</v>
+        <v>3107.351651027927</v>
       </c>
       <c r="P68" s="142" t="n">
-        <v>2163.155319482375</v>
+        <v>2163.15531948237</v>
       </c>
       <c r="Q68" s="143" t="n">
-        <v>372.0859813343213</v>
+        <v>372.085981334321</v>
       </c>
       <c r="R68" s="143" t="n">
-        <v>143.0165673943964</v>
+        <v>143.0165673943963</v>
       </c>
       <c r="S68" s="143" t="n">
-        <v>753.6182474419384</v>
+        <v>753.6182474419385</v>
       </c>
       <c r="T68" s="144" t="n">
-        <v>3431.876115653031</v>
+        <v>3431.876115653025</v>
       </c>
       <c r="V68" s="142" t="n">
-        <v>2378.866087308555</v>
+        <v>2378.86608730855</v>
       </c>
       <c r="W68" s="143" t="n">
-        <v>407.7078036315904</v>
+        <v>407.7078036315899</v>
       </c>
       <c r="X68" s="143" t="n">
         <v>157.7761316534635</v>
       </c>
       <c r="Y68" s="143" t="n">
-        <v>854.1693686244979</v>
+        <v>854.1693686244978</v>
       </c>
       <c r="Z68" s="144" t="n">
-        <v>3798.519391218107</v>
+        <v>3798.519391218101</v>
       </c>
       <c r="AE68" s="124" t="n">
         <v>20</v>
@@ -13735,49 +13735,49 @@
         <v>0</v>
       </c>
       <c r="J99" s="130" t="n">
-        <v>1964.875071784408</v>
+        <v>1964.875071784404</v>
       </c>
       <c r="K99" s="131" t="n">
-        <v>347.8756485030455</v>
+        <v>347.8756485030452</v>
       </c>
       <c r="L99" s="131" t="n">
         <v>130.6682137649017</v>
       </c>
       <c r="M99" s="131" t="n">
-        <v>663.9327169755762</v>
+        <v>663.9327169755763</v>
       </c>
       <c r="N99" s="132" t="n">
-        <v>3107.351651027931</v>
+        <v>3107.351651027927</v>
       </c>
       <c r="P99" s="130" t="n">
-        <v>2163.155319482375</v>
+        <v>2163.15531948237</v>
       </c>
       <c r="Q99" s="131" t="n">
-        <v>372.0859813343213</v>
+        <v>372.085981334321</v>
       </c>
       <c r="R99" s="131" t="n">
-        <v>143.0165673943964</v>
+        <v>143.0165673943963</v>
       </c>
       <c r="S99" s="131" t="n">
-        <v>753.6182474419384</v>
+        <v>753.6182474419385</v>
       </c>
       <c r="T99" s="132" t="n">
-        <v>3431.876115653031</v>
+        <v>3431.876115653025</v>
       </c>
       <c r="V99" s="130" t="n">
-        <v>2378.866087308555</v>
+        <v>2378.86608730855</v>
       </c>
       <c r="W99" s="131" t="n">
-        <v>407.7078036315904</v>
+        <v>407.7078036315899</v>
       </c>
       <c r="X99" s="131" t="n">
         <v>157.7761316534635</v>
       </c>
       <c r="Y99" s="131" t="n">
-        <v>854.1693686244979</v>
+        <v>854.1693686244978</v>
       </c>
       <c r="Z99" s="132" t="n">
-        <v>3798.519391218107</v>
+        <v>3798.519391218101</v>
       </c>
     </row>
     <row r="100">
@@ -14074,49 +14074,49 @@
         <v>0</v>
       </c>
       <c r="J104" s="142" t="n">
-        <v>1964.875071784408</v>
+        <v>1964.875071784404</v>
       </c>
       <c r="K104" s="143" t="n">
-        <v>347.8756485030455</v>
+        <v>347.8756485030452</v>
       </c>
       <c r="L104" s="143" t="n">
         <v>130.6682137649017</v>
       </c>
       <c r="M104" s="143" t="n">
-        <v>663.9327169755762</v>
+        <v>663.9327169755763</v>
       </c>
       <c r="N104" s="144" t="n">
-        <v>3107.351651027931</v>
+        <v>3107.351651027927</v>
       </c>
       <c r="P104" s="142" t="n">
-        <v>2163.155319482375</v>
+        <v>2163.15531948237</v>
       </c>
       <c r="Q104" s="143" t="n">
-        <v>372.0859813343213</v>
+        <v>372.085981334321</v>
       </c>
       <c r="R104" s="143" t="n">
-        <v>143.0165673943964</v>
+        <v>143.0165673943963</v>
       </c>
       <c r="S104" s="143" t="n">
-        <v>753.6182474419384</v>
+        <v>753.6182474419385</v>
       </c>
       <c r="T104" s="144" t="n">
-        <v>3431.876115653031</v>
+        <v>3431.876115653025</v>
       </c>
       <c r="V104" s="142" t="n">
-        <v>2378.866087308555</v>
+        <v>2378.86608730855</v>
       </c>
       <c r="W104" s="143" t="n">
-        <v>407.7078036315904</v>
+        <v>407.7078036315899</v>
       </c>
       <c r="X104" s="143" t="n">
         <v>157.7761316534635</v>
       </c>
       <c r="Y104" s="143" t="n">
-        <v>854.1693686244979</v>
+        <v>854.1693686244978</v>
       </c>
       <c r="Z104" s="144" t="n">
-        <v>3798.519391218107</v>
+        <v>3798.519391218101</v>
       </c>
     </row>
     <row r="105" ht="30.3" customHeight="1" thickBot="1"/>
@@ -15149,10 +15149,10 @@
         </is>
       </c>
       <c r="AH25" s="119" t="n">
-        <v>45226774.22397624</v>
+        <v>45226774.22397625</v>
       </c>
       <c r="AI25" s="46" t="n">
-        <v>57217.424704272</v>
+        <v>57217.42470427201</v>
       </c>
       <c r="AK25" s="120" t="n">
         <v>1</v>
@@ -15168,7 +15168,7 @@
         </is>
       </c>
       <c r="AN25" s="48" t="n">
-        <v>98.12243272919551</v>
+        <v>98.12243272919549</v>
       </c>
     </row>
     <row r="26">
@@ -15245,7 +15245,7 @@
         </is>
       </c>
       <c r="AN26" s="58" t="n">
-        <v>647.6879994047541</v>
+        <v>647.687999404754</v>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1" thickBot="1">
@@ -15460,7 +15460,7 @@
         <v>10521414.80268533</v>
       </c>
       <c r="AI29" s="56" t="n">
-        <v>508.3853589318974</v>
+        <v>508.3853589318973</v>
       </c>
       <c r="AK29" s="123" t="n">
         <v>5</v>
@@ -15668,10 +15668,10 @@
         </is>
       </c>
       <c r="AH32" s="122" t="n">
-        <v>9093847.954155255</v>
+        <v>9093847.954155257</v>
       </c>
       <c r="AI32" s="56" t="n">
-        <v>683.7286822945257</v>
+        <v>683.7286822945256</v>
       </c>
       <c r="AK32" s="123" t="n">
         <v>8</v>
@@ -15745,7 +15745,7 @@
         </is>
       </c>
       <c r="AH33" s="122" t="n">
-        <v>4604846.28437676</v>
+        <v>4604846.284376761</v>
       </c>
       <c r="AI33" s="56" t="n">
         <v>15719.43265046274</v>
@@ -15825,7 +15825,7 @@
         <v>3909046.280218133</v>
       </c>
       <c r="AI34" s="56" t="n">
-        <v>500.6658415511525</v>
+        <v>500.6658415511526</v>
       </c>
       <c r="AK34" s="123" t="n">
         <v>10</v>
@@ -15841,7 +15841,7 @@
         </is>
       </c>
       <c r="AN34" s="58" t="n">
-        <v>4318.464698316875</v>
+        <v>4318.464698316876</v>
       </c>
     </row>
     <row r="35" ht="15" customHeight="1" thickBot="1">
@@ -16133,7 +16133,7 @@
         <v>2569349.041505356</v>
       </c>
       <c r="AI38" s="56" t="n">
-        <v>2396.746329438651</v>
+        <v>2396.74632943865</v>
       </c>
       <c r="AK38" s="123" t="n">
         <v>14</v>
@@ -16196,7 +16196,7 @@
         <v>2565277.66149139</v>
       </c>
       <c r="AI39" s="56" t="n">
-        <v>8051.177706879998</v>
+        <v>8051.177706879999</v>
       </c>
       <c r="AK39" s="123" t="n">
         <v>15</v>
@@ -16340,7 +16340,7 @@
         <v>2204566.834283146</v>
       </c>
       <c r="AI41" s="56" t="n">
-        <v>397.0037510097246</v>
+        <v>397.0037510097247</v>
       </c>
       <c r="AK41" s="123" t="n">
         <v>17</v>
@@ -17252,7 +17252,7 @@
         <v>3237558.697110137</v>
       </c>
       <c r="AH56" s="56" t="n">
-        <v>761.1241252540833</v>
+        <v>761.1241252540834</v>
       </c>
     </row>
     <row r="57">
@@ -17330,7 +17330,7 @@
         </is>
       </c>
       <c r="AG57" s="122" t="n">
-        <v>2792867.850268204</v>
+        <v>2792867.850268205</v>
       </c>
       <c r="AH57" s="56" t="n">
         <v>8953.872484479998</v>
@@ -17573,7 +17573,7 @@
         </is>
       </c>
       <c r="AG60" s="122" t="n">
-        <v>1709553.141100613</v>
+        <v>1709553.141100614</v>
       </c>
       <c r="AH60" s="56" t="n">
         <v>430.9954658082593</v>
@@ -17763,49 +17763,49 @@
         <v>0</v>
       </c>
       <c r="J63" s="130" t="n">
-        <v>1964.875071784408</v>
+        <v>1964.875071784404</v>
       </c>
       <c r="K63" s="131" t="n">
-        <v>347.8756485030455</v>
+        <v>347.8756485030452</v>
       </c>
       <c r="L63" s="131" t="n">
         <v>130.6682137649017</v>
       </c>
       <c r="M63" s="131" t="n">
-        <v>663.9327169755762</v>
+        <v>663.9327169755763</v>
       </c>
       <c r="N63" s="132" t="n">
-        <v>3107.351651027931</v>
+        <v>3107.351651027927</v>
       </c>
       <c r="P63" s="130" t="n">
-        <v>2163.155319482375</v>
+        <v>2163.15531948237</v>
       </c>
       <c r="Q63" s="131" t="n">
-        <v>372.0859813343213</v>
+        <v>372.085981334321</v>
       </c>
       <c r="R63" s="131" t="n">
-        <v>143.0165673943964</v>
+        <v>143.0165673943963</v>
       </c>
       <c r="S63" s="131" t="n">
-        <v>753.6182474419384</v>
+        <v>753.6182474419385</v>
       </c>
       <c r="T63" s="132" t="n">
-        <v>3431.876115653031</v>
+        <v>3431.876115653025</v>
       </c>
       <c r="V63" s="130" t="n">
-        <v>2378.866087308555</v>
+        <v>2378.86608730855</v>
       </c>
       <c r="W63" s="131" t="n">
-        <v>407.7078036315904</v>
+        <v>407.7078036315899</v>
       </c>
       <c r="X63" s="131" t="n">
         <v>157.7761316534635</v>
       </c>
       <c r="Y63" s="131" t="n">
-        <v>854.1693686244979</v>
+        <v>854.1693686244978</v>
       </c>
       <c r="Z63" s="132" t="n">
-        <v>3798.519391218107</v>
+        <v>3798.519391218101</v>
       </c>
       <c r="AE63" s="121" t="n">
         <v>15</v>
@@ -17900,7 +17900,7 @@
         <v>884256.2432951636</v>
       </c>
       <c r="AH64" s="56" t="n">
-        <v>2379.392482130932</v>
+        <v>2379.392482130931</v>
       </c>
     </row>
     <row r="65">
@@ -18065,7 +18065,7 @@
         </is>
       </c>
       <c r="AG66" s="122" t="n">
-        <v>789302.3964713198</v>
+        <v>789302.39647132</v>
       </c>
       <c r="AH66" s="56" t="n">
         <v>555.2245665248699</v>
@@ -18174,49 +18174,49 @@
         <v>0</v>
       </c>
       <c r="J68" s="142" t="n">
-        <v>1964.875071784408</v>
+        <v>1964.875071784404</v>
       </c>
       <c r="K68" s="143" t="n">
-        <v>347.8756485030455</v>
+        <v>347.8756485030452</v>
       </c>
       <c r="L68" s="143" t="n">
         <v>130.6682137649017</v>
       </c>
       <c r="M68" s="143" t="n">
-        <v>663.9327169755762</v>
+        <v>663.9327169755763</v>
       </c>
       <c r="N68" s="144" t="n">
-        <v>3107.351651027931</v>
+        <v>3107.351651027927</v>
       </c>
       <c r="P68" s="142" t="n">
-        <v>2163.155319482375</v>
+        <v>2163.15531948237</v>
       </c>
       <c r="Q68" s="143" t="n">
-        <v>372.0859813343213</v>
+        <v>372.085981334321</v>
       </c>
       <c r="R68" s="143" t="n">
-        <v>143.0165673943964</v>
+        <v>143.0165673943963</v>
       </c>
       <c r="S68" s="143" t="n">
-        <v>753.6182474419384</v>
+        <v>753.6182474419385</v>
       </c>
       <c r="T68" s="144" t="n">
-        <v>3431.876115653031</v>
+        <v>3431.876115653025</v>
       </c>
       <c r="V68" s="142" t="n">
-        <v>2378.866087308555</v>
+        <v>2378.86608730855</v>
       </c>
       <c r="W68" s="143" t="n">
-        <v>407.7078036315904</v>
+        <v>407.7078036315899</v>
       </c>
       <c r="X68" s="143" t="n">
         <v>157.7761316534635</v>
       </c>
       <c r="Y68" s="143" t="n">
-        <v>854.1693686244979</v>
+        <v>854.1693686244978</v>
       </c>
       <c r="Z68" s="144" t="n">
-        <v>3798.519391218107</v>
+        <v>3798.519391218101</v>
       </c>
       <c r="AE68" s="124" t="n">
         <v>20</v>
@@ -20259,49 +20259,49 @@
         <v>0</v>
       </c>
       <c r="J99" s="130" t="n">
-        <v>1964.875071784408</v>
+        <v>1964.875071784404</v>
       </c>
       <c r="K99" s="131" t="n">
-        <v>347.8756485030455</v>
+        <v>347.8756485030452</v>
       </c>
       <c r="L99" s="131" t="n">
         <v>130.6682137649017</v>
       </c>
       <c r="M99" s="131" t="n">
-        <v>663.9327169755762</v>
+        <v>663.9327169755763</v>
       </c>
       <c r="N99" s="132" t="n">
-        <v>3107.351651027931</v>
+        <v>3107.351651027927</v>
       </c>
       <c r="P99" s="130" t="n">
-        <v>2163.155319482375</v>
+        <v>2163.15531948237</v>
       </c>
       <c r="Q99" s="131" t="n">
-        <v>372.0859813343213</v>
+        <v>372.085981334321</v>
       </c>
       <c r="R99" s="131" t="n">
-        <v>143.0165673943964</v>
+        <v>143.0165673943963</v>
       </c>
       <c r="S99" s="131" t="n">
-        <v>753.6182474419384</v>
+        <v>753.6182474419385</v>
       </c>
       <c r="T99" s="132" t="n">
-        <v>3431.876115653031</v>
+        <v>3431.876115653025</v>
       </c>
       <c r="V99" s="130" t="n">
-        <v>2378.866087308555</v>
+        <v>2378.86608730855</v>
       </c>
       <c r="W99" s="131" t="n">
-        <v>407.7078036315904</v>
+        <v>407.7078036315899</v>
       </c>
       <c r="X99" s="131" t="n">
         <v>157.7761316534635</v>
       </c>
       <c r="Y99" s="131" t="n">
-        <v>854.1693686244979</v>
+        <v>854.1693686244978</v>
       </c>
       <c r="Z99" s="132" t="n">
-        <v>3798.519391218107</v>
+        <v>3798.519391218101</v>
       </c>
     </row>
     <row r="100">
@@ -20598,49 +20598,49 @@
         <v>0</v>
       </c>
       <c r="J104" s="142" t="n">
-        <v>1964.875071784408</v>
+        <v>1964.875071784404</v>
       </c>
       <c r="K104" s="143" t="n">
-        <v>347.8756485030455</v>
+        <v>347.8756485030452</v>
       </c>
       <c r="L104" s="143" t="n">
         <v>130.6682137649017</v>
       </c>
       <c r="M104" s="143" t="n">
-        <v>663.9327169755762</v>
+        <v>663.9327169755763</v>
       </c>
       <c r="N104" s="144" t="n">
-        <v>3107.351651027931</v>
+        <v>3107.351651027927</v>
       </c>
       <c r="P104" s="142" t="n">
-        <v>2163.155319482375</v>
+        <v>2163.15531948237</v>
       </c>
       <c r="Q104" s="143" t="n">
-        <v>372.0859813343213</v>
+        <v>372.085981334321</v>
       </c>
       <c r="R104" s="143" t="n">
-        <v>143.0165673943964</v>
+        <v>143.0165673943963</v>
       </c>
       <c r="S104" s="143" t="n">
-        <v>753.6182474419384</v>
+        <v>753.6182474419385</v>
       </c>
       <c r="T104" s="144" t="n">
-        <v>3431.876115653031</v>
+        <v>3431.876115653025</v>
       </c>
       <c r="V104" s="142" t="n">
-        <v>2378.866087308555</v>
+        <v>2378.86608730855</v>
       </c>
       <c r="W104" s="143" t="n">
-        <v>407.7078036315904</v>
+        <v>407.7078036315899</v>
       </c>
       <c r="X104" s="143" t="n">
         <v>157.7761316534635</v>
       </c>
       <c r="Y104" s="143" t="n">
-        <v>854.1693686244979</v>
+        <v>854.1693686244978</v>
       </c>
       <c r="Z104" s="144" t="n">
-        <v>3798.519391218107</v>
+        <v>3798.519391218101</v>
       </c>
     </row>
     <row r="105" ht="30.3" customHeight="1" thickBot="1"/>
@@ -22000,7 +22000,7 @@
         </is>
       </c>
       <c r="AN29" s="58" t="n">
-        <v>238.950440935838</v>
+        <v>238.9504409358379</v>
       </c>
     </row>
     <row r="30" ht="15.6" customHeight="1" thickBot="1" thickTop="1">
@@ -22195,7 +22195,7 @@
         <v>9352525.180961719</v>
       </c>
       <c r="AI32" s="56" t="n">
-        <v>697.3417203590096</v>
+        <v>697.3417203590097</v>
       </c>
       <c r="AK32" s="123" t="n">
         <v>8</v>
@@ -22269,10 +22269,10 @@
         </is>
       </c>
       <c r="AH33" s="122" t="n">
-        <v>5249960.052605657</v>
+        <v>5249960.052605658</v>
       </c>
       <c r="AI33" s="56" t="n">
-        <v>17635.78868488064</v>
+        <v>17635.78868488065</v>
       </c>
       <c r="AK33" s="123" t="n">
         <v>9</v>
@@ -23018,7 +23018,7 @@
         <v>2006758.971569033</v>
       </c>
       <c r="AI43" s="56" t="n">
-        <v>3570.123843302602</v>
+        <v>3570.123843302601</v>
       </c>
       <c r="AK43" s="123" t="n">
         <v>19</v>
@@ -23095,7 +23095,7 @@
         <v>1951341.934311199</v>
       </c>
       <c r="AI44" s="84" t="n">
-        <v>2751.314133569149</v>
+        <v>2751.314133569148</v>
       </c>
       <c r="AK44" s="126" t="n">
         <v>20</v>
@@ -24287,49 +24287,49 @@
         <v>0</v>
       </c>
       <c r="J63" s="130" t="n">
-        <v>1964.875071784408</v>
+        <v>1964.875071784404</v>
       </c>
       <c r="K63" s="131" t="n">
-        <v>347.8756485030455</v>
+        <v>347.8756485030452</v>
       </c>
       <c r="L63" s="131" t="n">
         <v>130.6682137649017</v>
       </c>
       <c r="M63" s="131" t="n">
-        <v>663.9327169755762</v>
+        <v>663.9327169755763</v>
       </c>
       <c r="N63" s="132" t="n">
-        <v>3107.351651027931</v>
+        <v>3107.351651027927</v>
       </c>
       <c r="P63" s="130" t="n">
-        <v>2163.155319482375</v>
+        <v>2163.15531948237</v>
       </c>
       <c r="Q63" s="131" t="n">
-        <v>372.0859813343213</v>
+        <v>372.085981334321</v>
       </c>
       <c r="R63" s="131" t="n">
-        <v>143.0165673943964</v>
+        <v>143.0165673943963</v>
       </c>
       <c r="S63" s="131" t="n">
-        <v>753.6182474419384</v>
+        <v>753.6182474419385</v>
       </c>
       <c r="T63" s="132" t="n">
-        <v>3431.876115653031</v>
+        <v>3431.876115653025</v>
       </c>
       <c r="V63" s="130" t="n">
-        <v>2378.866087308555</v>
+        <v>2378.86608730855</v>
       </c>
       <c r="W63" s="131" t="n">
-        <v>407.7078036315904</v>
+        <v>407.7078036315899</v>
       </c>
       <c r="X63" s="131" t="n">
         <v>157.7761316534635</v>
       </c>
       <c r="Y63" s="131" t="n">
-        <v>854.1693686244979</v>
+        <v>854.1693686244978</v>
       </c>
       <c r="Z63" s="132" t="n">
-        <v>3798.519391218107</v>
+        <v>3798.519391218101</v>
       </c>
       <c r="AE63" s="121" t="n">
         <v>15</v>
@@ -24507,7 +24507,7 @@
         </is>
       </c>
       <c r="AG65" s="122" t="n">
-        <v>769221.9314309078</v>
+        <v>769221.9314309077</v>
       </c>
       <c r="AH65" s="56" t="n">
         <v>2303.581052657972</v>
@@ -24670,7 +24670,7 @@
         </is>
       </c>
       <c r="AG67" s="122" t="n">
-        <v>518402.8556809943</v>
+        <v>518402.8556809945</v>
       </c>
       <c r="AH67" s="56" t="n">
         <v>3956.458053460796</v>
@@ -24698,49 +24698,49 @@
         <v>0</v>
       </c>
       <c r="J68" s="142" t="n">
-        <v>1964.875071784408</v>
+        <v>1964.875071784404</v>
       </c>
       <c r="K68" s="143" t="n">
-        <v>347.8756485030455</v>
+        <v>347.8756485030452</v>
       </c>
       <c r="L68" s="143" t="n">
         <v>130.6682137649017</v>
       </c>
       <c r="M68" s="143" t="n">
-        <v>663.9327169755762</v>
+        <v>663.9327169755763</v>
       </c>
       <c r="N68" s="144" t="n">
-        <v>3107.351651027931</v>
+        <v>3107.351651027927</v>
       </c>
       <c r="P68" s="142" t="n">
-        <v>2163.155319482375</v>
+        <v>2163.15531948237</v>
       </c>
       <c r="Q68" s="143" t="n">
-        <v>372.0859813343213</v>
+        <v>372.085981334321</v>
       </c>
       <c r="R68" s="143" t="n">
-        <v>143.0165673943964</v>
+        <v>143.0165673943963</v>
       </c>
       <c r="S68" s="143" t="n">
-        <v>753.6182474419384</v>
+        <v>753.6182474419385</v>
       </c>
       <c r="T68" s="144" t="n">
-        <v>3431.876115653031</v>
+        <v>3431.876115653025</v>
       </c>
       <c r="V68" s="142" t="n">
-        <v>2378.866087308555</v>
+        <v>2378.86608730855</v>
       </c>
       <c r="W68" s="143" t="n">
-        <v>407.7078036315904</v>
+        <v>407.7078036315899</v>
       </c>
       <c r="X68" s="143" t="n">
         <v>157.7761316534635</v>
       </c>
       <c r="Y68" s="143" t="n">
-        <v>854.1693686244979</v>
+        <v>854.1693686244978</v>
       </c>
       <c r="Z68" s="144" t="n">
-        <v>3798.519391218107</v>
+        <v>3798.519391218101</v>
       </c>
       <c r="AE68" s="124" t="n">
         <v>20</v>
@@ -24751,7 +24751,7 @@
         </is>
       </c>
       <c r="AG68" s="125" t="n">
-        <v>442089.1120680772</v>
+        <v>442089.1120680771</v>
       </c>
       <c r="AH68" s="84" t="n">
         <v>234.9247334314719</v>
@@ -26783,49 +26783,49 @@
         <v>0</v>
       </c>
       <c r="J99" s="130" t="n">
-        <v>1964.875071784408</v>
+        <v>1964.875071784404</v>
       </c>
       <c r="K99" s="131" t="n">
-        <v>347.8756485030455</v>
+        <v>347.8756485030452</v>
       </c>
       <c r="L99" s="131" t="n">
         <v>130.6682137649017</v>
       </c>
       <c r="M99" s="131" t="n">
-        <v>663.9327169755762</v>
+        <v>663.9327169755763</v>
       </c>
       <c r="N99" s="132" t="n">
-        <v>3107.351651027931</v>
+        <v>3107.351651027927</v>
       </c>
       <c r="P99" s="130" t="n">
-        <v>2163.155319482375</v>
+        <v>2163.15531948237</v>
       </c>
       <c r="Q99" s="131" t="n">
-        <v>372.0859813343213</v>
+        <v>372.085981334321</v>
       </c>
       <c r="R99" s="131" t="n">
-        <v>143.0165673943964</v>
+        <v>143.0165673943963</v>
       </c>
       <c r="S99" s="131" t="n">
-        <v>753.6182474419384</v>
+        <v>753.6182474419385</v>
       </c>
       <c r="T99" s="132" t="n">
-        <v>3431.876115653031</v>
+        <v>3431.876115653025</v>
       </c>
       <c r="V99" s="130" t="n">
-        <v>2378.866087308555</v>
+        <v>2378.86608730855</v>
       </c>
       <c r="W99" s="131" t="n">
-        <v>407.7078036315904</v>
+        <v>407.7078036315899</v>
       </c>
       <c r="X99" s="131" t="n">
         <v>157.7761316534635</v>
       </c>
       <c r="Y99" s="131" t="n">
-        <v>854.1693686244979</v>
+        <v>854.1693686244978</v>
       </c>
       <c r="Z99" s="132" t="n">
-        <v>3798.519391218107</v>
+        <v>3798.519391218101</v>
       </c>
     </row>
     <row r="100">
@@ -27122,49 +27122,49 @@
         <v>0</v>
       </c>
       <c r="J104" s="142" t="n">
-        <v>1964.875071784408</v>
+        <v>1964.875071784404</v>
       </c>
       <c r="K104" s="143" t="n">
-        <v>347.8756485030455</v>
+        <v>347.8756485030452</v>
       </c>
       <c r="L104" s="143" t="n">
         <v>130.6682137649017</v>
       </c>
       <c r="M104" s="143" t="n">
-        <v>663.9327169755762</v>
+        <v>663.9327169755763</v>
       </c>
       <c r="N104" s="144" t="n">
-        <v>3107.351651027931</v>
+        <v>3107.351651027927</v>
       </c>
       <c r="P104" s="142" t="n">
-        <v>2163.155319482375</v>
+        <v>2163.15531948237</v>
       </c>
       <c r="Q104" s="143" t="n">
-        <v>372.0859813343213</v>
+        <v>372.085981334321</v>
       </c>
       <c r="R104" s="143" t="n">
-        <v>143.0165673943964</v>
+        <v>143.0165673943963</v>
       </c>
       <c r="S104" s="143" t="n">
-        <v>753.6182474419384</v>
+        <v>753.6182474419385</v>
       </c>
       <c r="T104" s="144" t="n">
-        <v>3431.876115653031</v>
+        <v>3431.876115653025</v>
       </c>
       <c r="V104" s="142" t="n">
-        <v>2378.866087308555</v>
+        <v>2378.86608730855</v>
       </c>
       <c r="W104" s="143" t="n">
-        <v>407.7078036315904</v>
+        <v>407.7078036315899</v>
       </c>
       <c r="X104" s="143" t="n">
         <v>157.7761316534635</v>
       </c>
       <c r="Y104" s="143" t="n">
-        <v>854.1693686244979</v>
+        <v>854.1693686244978</v>
       </c>
       <c r="Z104" s="144" t="n">
-        <v>3798.519391218107</v>
+        <v>3798.519391218101</v>
       </c>
     </row>
     <row r="105" ht="30.3" customHeight="1" thickBot="1"/>
@@ -28197,10 +28197,10 @@
         </is>
       </c>
       <c r="AH25" s="119" t="n">
-        <v>69272501.28316741</v>
+        <v>69272501.28316739</v>
       </c>
       <c r="AI25" s="46" t="n">
-        <v>82393.09157415169</v>
+        <v>82393.09157415168</v>
       </c>
       <c r="AK25" s="120" t="n">
         <v>1</v>
@@ -28216,7 +28216,7 @@
         </is>
       </c>
       <c r="AN25" s="48" t="n">
-        <v>699.3946957278139</v>
+        <v>699.394695727814</v>
       </c>
     </row>
     <row r="26">
@@ -28293,7 +28293,7 @@
         </is>
       </c>
       <c r="AN26" s="58" t="n">
-        <v>96.24752498419528</v>
+        <v>96.24752498419527</v>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1" thickBot="1">
@@ -28354,7 +28354,7 @@
         <v>19863574.56683607</v>
       </c>
       <c r="AI27" s="56" t="n">
-        <v>1141.429155052514</v>
+        <v>1141.429155052513</v>
       </c>
       <c r="AK27" s="123" t="n">
         <v>3</v>
@@ -28431,7 +28431,7 @@
         <v>16598675.10338615</v>
       </c>
       <c r="AI28" s="56" t="n">
-        <v>7591.883513651961</v>
+        <v>7591.88351365196</v>
       </c>
       <c r="AK28" s="123" t="n">
         <v>4</v>
@@ -28505,7 +28505,7 @@
         </is>
       </c>
       <c r="AH29" s="122" t="n">
-        <v>14570481.40100322</v>
+        <v>14570481.40100323</v>
       </c>
       <c r="AI29" s="56" t="n">
         <v>1523.105781032218</v>
@@ -28585,7 +28585,7 @@
         <v>11245700.87172257</v>
       </c>
       <c r="AI30" s="56" t="n">
-        <v>528.8307919987676</v>
+        <v>528.8307919987677</v>
       </c>
       <c r="AK30" s="123" t="n">
         <v>6</v>
@@ -28793,7 +28793,7 @@
         </is>
       </c>
       <c r="AH33" s="122" t="n">
-        <v>6042412.593942055</v>
+        <v>6042412.593942057</v>
       </c>
       <c r="AI33" s="56" t="n">
         <v>19785.76768345445</v>
@@ -28870,10 +28870,10 @@
         </is>
       </c>
       <c r="AH34" s="122" t="n">
-        <v>5241847.482288073</v>
+        <v>5241847.482288072</v>
       </c>
       <c r="AI34" s="56" t="n">
-        <v>15780.3083054848</v>
+        <v>15780.30830548479</v>
       </c>
       <c r="AK34" s="123" t="n">
         <v>10</v>
@@ -29462,10 +29462,10 @@
         </is>
       </c>
       <c r="AH42" s="122" t="n">
-        <v>2478636.557893779</v>
+        <v>2478636.55789378</v>
       </c>
       <c r="AI42" s="56" t="n">
-        <v>412.9698158775625</v>
+        <v>412.9698158775626</v>
       </c>
       <c r="AK42" s="123" t="n">
         <v>18</v>
@@ -30300,7 +30300,7 @@
         <v>3500805.438701428</v>
       </c>
       <c r="AH56" s="56" t="n">
-        <v>772.8172375441062</v>
+        <v>772.8172375441061</v>
       </c>
     </row>
     <row r="57">
@@ -30543,7 +30543,7 @@
         <v>2639799.608883559</v>
       </c>
       <c r="AH59" s="56" t="n">
-        <v>6042.247586441125</v>
+        <v>6042.247586441126</v>
       </c>
     </row>
     <row r="60">
@@ -30705,7 +30705,7 @@
         <v>1291690.181123719</v>
       </c>
       <c r="AH61" s="56" t="n">
-        <v>285.5684684503163</v>
+        <v>285.5684684503162</v>
       </c>
     </row>
     <row r="62">
@@ -30811,49 +30811,49 @@
         <v>0</v>
       </c>
       <c r="J63" s="130" t="n">
-        <v>1964.875071784408</v>
+        <v>1964.875071784404</v>
       </c>
       <c r="K63" s="131" t="n">
-        <v>347.8756485030455</v>
+        <v>347.8756485030452</v>
       </c>
       <c r="L63" s="131" t="n">
         <v>130.6682137649017</v>
       </c>
       <c r="M63" s="131" t="n">
-        <v>663.9327169755762</v>
+        <v>663.9327169755763</v>
       </c>
       <c r="N63" s="132" t="n">
-        <v>3107.351651027931</v>
+        <v>3107.351651027927</v>
       </c>
       <c r="P63" s="130" t="n">
-        <v>2163.155319482375</v>
+        <v>2163.15531948237</v>
       </c>
       <c r="Q63" s="131" t="n">
-        <v>372.0859813343213</v>
+        <v>372.085981334321</v>
       </c>
       <c r="R63" s="131" t="n">
-        <v>143.0165673943964</v>
+        <v>143.0165673943963</v>
       </c>
       <c r="S63" s="131" t="n">
-        <v>753.6182474419384</v>
+        <v>753.6182474419385</v>
       </c>
       <c r="T63" s="132" t="n">
-        <v>3431.876115653031</v>
+        <v>3431.876115653025</v>
       </c>
       <c r="V63" s="130" t="n">
-        <v>2378.866087308555</v>
+        <v>2378.86608730855</v>
       </c>
       <c r="W63" s="131" t="n">
-        <v>407.7078036315904</v>
+        <v>407.7078036315899</v>
       </c>
       <c r="X63" s="131" t="n">
         <v>157.7761316534635</v>
       </c>
       <c r="Y63" s="131" t="n">
-        <v>854.1693686244979</v>
+        <v>854.1693686244978</v>
       </c>
       <c r="Z63" s="132" t="n">
-        <v>3798.519391218107</v>
+        <v>3798.519391218101</v>
       </c>
       <c r="AE63" s="121" t="n">
         <v>15</v>
@@ -31222,49 +31222,49 @@
         <v>0</v>
       </c>
       <c r="J68" s="142" t="n">
-        <v>1964.875071784408</v>
+        <v>1964.875071784404</v>
       </c>
       <c r="K68" s="143" t="n">
-        <v>347.8756485030455</v>
+        <v>347.8756485030452</v>
       </c>
       <c r="L68" s="143" t="n">
         <v>130.6682137649017</v>
       </c>
       <c r="M68" s="143" t="n">
-        <v>663.9327169755762</v>
+        <v>663.9327169755763</v>
       </c>
       <c r="N68" s="144" t="n">
-        <v>3107.351651027931</v>
+        <v>3107.351651027927</v>
       </c>
       <c r="P68" s="142" t="n">
-        <v>2163.155319482375</v>
+        <v>2163.15531948237</v>
       </c>
       <c r="Q68" s="143" t="n">
-        <v>372.0859813343213</v>
+        <v>372.085981334321</v>
       </c>
       <c r="R68" s="143" t="n">
-        <v>143.0165673943964</v>
+        <v>143.0165673943963</v>
       </c>
       <c r="S68" s="143" t="n">
-        <v>753.6182474419384</v>
+        <v>753.6182474419385</v>
       </c>
       <c r="T68" s="144" t="n">
-        <v>3431.876115653031</v>
+        <v>3431.876115653025</v>
       </c>
       <c r="V68" s="142" t="n">
-        <v>2378.866087308555</v>
+        <v>2378.86608730855</v>
       </c>
       <c r="W68" s="143" t="n">
-        <v>407.7078036315904</v>
+        <v>407.7078036315899</v>
       </c>
       <c r="X68" s="143" t="n">
         <v>157.7761316534635</v>
       </c>
       <c r="Y68" s="143" t="n">
-        <v>854.1693686244979</v>
+        <v>854.1693686244978</v>
       </c>
       <c r="Z68" s="144" t="n">
-        <v>3798.519391218107</v>
+        <v>3798.519391218101</v>
       </c>
       <c r="AE68" s="124" t="n">
         <v>20</v>
@@ -31278,7 +31278,7 @@
         <v>522946.3976335505</v>
       </c>
       <c r="AH68" s="84" t="n">
-        <v>262.1994949828658</v>
+        <v>262.1994949828659</v>
       </c>
     </row>
     <row r="69" ht="15" customHeight="1" thickBot="1">
@@ -33307,49 +33307,49 @@
         <v>0</v>
       </c>
       <c r="J99" s="130" t="n">
-        <v>1964.875071784408</v>
+        <v>1964.875071784404</v>
       </c>
       <c r="K99" s="131" t="n">
-        <v>347.8756485030455</v>
+        <v>347.8756485030452</v>
       </c>
       <c r="L99" s="131" t="n">
         <v>130.6682137649017</v>
       </c>
       <c r="M99" s="131" t="n">
-        <v>663.9327169755762</v>
+        <v>663.9327169755763</v>
       </c>
       <c r="N99" s="132" t="n">
-        <v>3107.351651027931</v>
+        <v>3107.351651027927</v>
       </c>
       <c r="P99" s="130" t="n">
-        <v>2163.155319482375</v>
+        <v>2163.15531948237</v>
       </c>
       <c r="Q99" s="131" t="n">
-        <v>372.0859813343213</v>
+        <v>372.085981334321</v>
       </c>
       <c r="R99" s="131" t="n">
-        <v>143.0165673943964</v>
+        <v>143.0165673943963</v>
       </c>
       <c r="S99" s="131" t="n">
-        <v>753.6182474419384</v>
+        <v>753.6182474419385</v>
       </c>
       <c r="T99" s="132" t="n">
-        <v>3431.876115653031</v>
+        <v>3431.876115653025</v>
       </c>
       <c r="V99" s="130" t="n">
-        <v>2378.866087308555</v>
+        <v>2378.86608730855</v>
       </c>
       <c r="W99" s="131" t="n">
-        <v>407.7078036315904</v>
+        <v>407.7078036315899</v>
       </c>
       <c r="X99" s="131" t="n">
         <v>157.7761316534635</v>
       </c>
       <c r="Y99" s="131" t="n">
-        <v>854.1693686244979</v>
+        <v>854.1693686244978</v>
       </c>
       <c r="Z99" s="132" t="n">
-        <v>3798.519391218107</v>
+        <v>3798.519391218101</v>
       </c>
     </row>
     <row r="100">
@@ -33646,49 +33646,49 @@
         <v>0</v>
       </c>
       <c r="J104" s="142" t="n">
-        <v>1964.875071784408</v>
+        <v>1964.875071784404</v>
       </c>
       <c r="K104" s="143" t="n">
-        <v>347.8756485030455</v>
+        <v>347.8756485030452</v>
       </c>
       <c r="L104" s="143" t="n">
         <v>130.6682137649017</v>
       </c>
       <c r="M104" s="143" t="n">
-        <v>663.9327169755762</v>
+        <v>663.9327169755763</v>
       </c>
       <c r="N104" s="144" t="n">
-        <v>3107.351651027931</v>
+        <v>3107.351651027927</v>
       </c>
       <c r="P104" s="142" t="n">
-        <v>2163.155319482375</v>
+        <v>2163.15531948237</v>
       </c>
       <c r="Q104" s="143" t="n">
-        <v>372.0859813343213</v>
+        <v>372.085981334321</v>
       </c>
       <c r="R104" s="143" t="n">
-        <v>143.0165673943964</v>
+        <v>143.0165673943963</v>
       </c>
       <c r="S104" s="143" t="n">
-        <v>753.6182474419384</v>
+        <v>753.6182474419385</v>
       </c>
       <c r="T104" s="144" t="n">
-        <v>3431.876115653031</v>
+        <v>3431.876115653025</v>
       </c>
       <c r="V104" s="142" t="n">
-        <v>2378.866087308555</v>
+        <v>2378.86608730855</v>
       </c>
       <c r="W104" s="143" t="n">
-        <v>407.7078036315904</v>
+        <v>407.7078036315899</v>
       </c>
       <c r="X104" s="143" t="n">
         <v>157.7761316534635</v>
       </c>
       <c r="Y104" s="143" t="n">
-        <v>854.1693686244979</v>
+        <v>854.1693686244978</v>
       </c>
       <c r="Z104" s="144" t="n">
-        <v>3798.519391218107</v>
+        <v>3798.519391218101</v>
       </c>
     </row>
     <row r="105" ht="30.3" customHeight="1" thickBot="1"/>
